--- a/output/graficos_dimensiones/comunal_d_depmen_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:07</t>
+    <t xml:space="preserve">2026-09-10 01:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:19</t>
+    <t xml:space="preserve">2026-09-12 22:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:31</t>
+    <t xml:space="preserve">2026-09-24 00:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
